--- a/data/trans_bre/IP16A09-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A09-Habitat-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,57</t>
+          <t>0,0; 9,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,37; 0,0</t>
+          <t>-14,02; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,48</t>
+          <t>0,0; 10,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,07</t>
+          <t>0,0; 7,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 7,51</t>
+          <t>-2,5; 7,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,35</t>
+          <t>0,0; 6,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,22 +794,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 16,76</t>
+          <t>-4,59; 17,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 5,41</t>
+          <t>-4,71; 4,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,81; 2,51</t>
+          <t>-15,53; 2,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-63,28; —</t>
+          <t>-86,84; 1085,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 7,67</t>
+          <t>-6,91; 8,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 2,18</t>
+          <t>-8,59; 2,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 5,67</t>
+          <t>-1,09; 5,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 1,55</t>
+          <t>-4,01; 1,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 1,67</t>
+          <t>-2,77; 1,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-42,38; 504,44</t>
+          <t>-44,35; 560,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-83,39; 138,99</t>
+          <t>-87,85; 117,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-88,19; 351,06</t>
+          <t>-87,21; 352,95</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A09-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A09-Habitat-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,2</t>
+          <t>0,0; 9,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,02; 0,0</t>
+          <t>-14,77; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,06</t>
+          <t>0,0; 11,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,96</t>
+          <t>0,0; 8,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 7,26</t>
+          <t>-1,98; 8,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,37</t>
+          <t>0,0; 5,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,22 +794,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 17,71</t>
+          <t>-4,16; 17,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 4,81</t>
+          <t>-4,7; 5,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,53; 2,94</t>
+          <t>-17,4; 2,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-86,84; 1085,18</t>
+          <t>-62,94; 893,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 8,83</t>
+          <t>-6,85; 7,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 2,02</t>
+          <t>-8,28; 1,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 5,01</t>
+          <t>-1,44; 5,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 1,39</t>
+          <t>-3,71; 1,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 1,63</t>
+          <t>-3,06; 1,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-44,35; 560,33</t>
+          <t>-57,47; 388,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-87,85; 117,43</t>
+          <t>-86,19; 118,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-87,21; 352,95</t>
+          <t>-89,78; 418,88</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A09-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A09-Habitat-trans_bre.xlsx
@@ -520,7 +520,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para los vómitos</t>
+          <t>Menores que consumieron medicamentos para los vómitos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,14</t>
+          <t>0,0; 10,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 0,0</t>
+          <t>-14,37; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,07</t>
+          <t>0,0; 7,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,99</t>
+          <t>0,0; 9,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 8,02</t>
+          <t>-1,37; 7,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,37</t>
+          <t>0,0; 5,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,22 +794,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 17,32</t>
+          <t>-4,26; 16,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 5,18</t>
+          <t>-4,62; 5,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,4; 2,73</t>
+          <t>-17,81; 2,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-62,94; 893,75</t>
+          <t>-63,28; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 7,69</t>
+          <t>-6,95; 7,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 1,94</t>
+          <t>-9,47; 2,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 5,11</t>
+          <t>-0,97; 5,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 1,37</t>
+          <t>-3,57; 1,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 1,51</t>
+          <t>-2,69; 1,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-57,47; 388,41</t>
+          <t>-42,38; 504,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-86,19; 118,52</t>
+          <t>-83,39; 138,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-89,78; 418,88</t>
+          <t>-88,19; 351,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A09-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A09-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,34 +603,26 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,82</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-4,16</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,75</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
+      <c r="C4" s="5" t="n">
+        <v>0.4307123003897781</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.058480975090749</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.4184760717194209</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -629,204 +630,120 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 10,57</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-14,37; 0,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,48</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-4.154853734382413</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2.813235407871622</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>2.326408371930965</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2,51</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,8</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,06</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>141,97%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 9,07</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-1,37; 7,51</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,35</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+      <c r="C7" s="5" t="n">
+        <v>0.5363566102981179</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.4827735836358945</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.272161427240995</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1.670756754045247</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>5,45</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,18</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-5,25</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>98,9%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,49%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-60,71%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-0.3993706155023096</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-4,26; 16,76</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-4,62; 5,41</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-17,81; 2,51</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-63,28; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.877240781343802</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.24126874898396</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.521581616797303</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,157 +751,217 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,35</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-2,58</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-10,25%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-62,5%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.7084283098752968</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.01975680898472811</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.9400385475328326</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0.5474183575681963</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.02654779943383035</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.5598169123763382</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-6,95; 7,67</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-9,47; 2,18</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-1.417995834528271</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-1.533364444710692</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-3.384287670809464</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-0.7794903149708827</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>3.065173478266404</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.421656847984457</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.6643807605951934</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>8.499405552340837</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.2638073596193508</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.6230898756191029</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.4105285699245745</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.6248764312409625</v>
+      </c>
+      <c r="H13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.318469857759569</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.025089263116266</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.8801566207410491</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.4371693783503763</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,87</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-1,04</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,49</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>82,41%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-35,78%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-25,87%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-0,97; 5,67</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-3,57; 1,55</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-2,69; 1,67</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-42,38; 504,44</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-83,39; 138,99</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-88,19; 351,06</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>0.3103423196200105</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.2504567071346651</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.05253578108600039</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>0.6854163619975722</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.3371196004354387</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.1398155768639447</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.2931731909522857</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-0.9310440924440256</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.5858416377280756</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-0.523641314510919</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.8673957106887953</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.9108660836075521</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.386916849020458</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.3923913423397534</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>5.302899561701142</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>1.430324878230701</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>3.381147932873942</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -993,13 +970,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
